--- a/output/yearly_benthic_cover_iteration_80_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_80_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.21025038877007</v>
+        <v>45.44238459795949</v>
       </c>
       <c r="M2" t="n">
-        <v>99.94717731788029</v>
+        <v>100.548275403597</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.10029653291538</v>
+        <v>88.01057461022427</v>
       </c>
       <c r="C3" t="n">
-        <v>45.96904108527107</v>
+        <v>45.90836689548705</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228887118411074</v>
+        <v>2.228703092105968</v>
       </c>
       <c r="E3" t="n">
-        <v>5.733360987407137</v>
+        <v>5.69387494389947</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429623728036913</v>
+        <v>0.7429010307019894</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98637432165729</v>
+        <v>33.9662372889206</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17626914896979</v>
+        <v>34.17344741229151</v>
       </c>
       <c r="I3" t="n">
-        <v>6.588927753643312</v>
+        <v>6.562279400417291</v>
       </c>
       <c r="J3" t="n">
-        <v>4.64351483002307</v>
+        <v>4.643131441887434</v>
       </c>
       <c r="K3" t="n">
-        <v>11.89970346708462</v>
+        <v>11.98942538977574</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89476333642997</v>
+        <v>48.86665262716504</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7635078887857</v>
+        <v>106.7644449124278</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.23917223750756</v>
+        <v>87.0291369579995</v>
       </c>
       <c r="C4" t="n">
-        <v>42.74558935954407</v>
+        <v>42.56170639790567</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187722156230822</v>
+        <v>2.181053791259174</v>
       </c>
       <c r="E4" t="n">
-        <v>6.544525264263259</v>
+        <v>6.485481564339393</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445243677526632</v>
+        <v>0.74446032862147</v>
       </c>
       <c r="G4" t="n">
-        <v>33.35868537229844</v>
+        <v>33.24004479385656</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2481209166225</v>
+        <v>34.24517511658762</v>
       </c>
       <c r="I4" t="n">
-        <v>5.502316861885734</v>
+        <v>5.480044309451108</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653277298454145</v>
+        <v>4.652877053884188</v>
       </c>
       <c r="K4" t="n">
-        <v>12.76082776249243</v>
+        <v>12.9708630420005</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31055710702896</v>
+        <v>44.28514502119335</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81697422906547</v>
+        <v>99.81771446109951</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.08874509166591</v>
+        <v>85.77547794229123</v>
       </c>
       <c r="C5" t="n">
-        <v>42.44924068996541</v>
+        <v>42.15849872756986</v>
       </c>
       <c r="D5" t="n">
-        <v>2.131712096163249</v>
+        <v>2.119567875725339</v>
       </c>
       <c r="E5" t="n">
-        <v>7.142542205736923</v>
+        <v>7.065120265786818</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458485487998247</v>
+        <v>0.7457838513320966</v>
       </c>
       <c r="G5" t="n">
-        <v>32.50463634867985</v>
+        <v>32.30297731082304</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30903324479193</v>
+        <v>34.30605716127643</v>
       </c>
       <c r="I5" t="n">
-        <v>4.593419217495226</v>
+        <v>4.574822406521896</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661553429998905</v>
+        <v>4.661149070825604</v>
       </c>
       <c r="K5" t="n">
-        <v>13.9112549083341</v>
+        <v>14.22452205770877</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48666226664809</v>
+        <v>43.46475576168106</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8471578649476</v>
+        <v>99.84777654695969</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.65816514790909</v>
+        <v>84.3312150917108</v>
       </c>
       <c r="C6" t="n">
-        <v>41.73213414694179</v>
+        <v>41.42457845399269</v>
       </c>
       <c r="D6" t="n">
-        <v>2.061826205612696</v>
+        <v>2.048869206593518</v>
       </c>
       <c r="E6" t="n">
-        <v>7.547319519026603</v>
+        <v>7.465812486333509</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469743726193161</v>
+        <v>0.7469093663297198</v>
       </c>
       <c r="G6" t="n">
-        <v>31.43900677218219</v>
+        <v>31.2255041470589</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36082114048854</v>
+        <v>34.35783085116711</v>
       </c>
       <c r="I6" t="n">
-        <v>3.833627309109019</v>
+        <v>3.818105494667313</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668589828870726</v>
+        <v>4.66818353956075</v>
       </c>
       <c r="K6" t="n">
-        <v>15.34183485209093</v>
+        <v>15.66878490828919</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79843602270353</v>
+        <v>42.77955823753695</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87240502173624</v>
+        <v>99.87292159981882</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.97395324519303</v>
+        <v>82.70623088699385</v>
       </c>
       <c r="C7" t="n">
-        <v>40.64336320410104</v>
+        <v>40.39240343141359</v>
       </c>
       <c r="D7" t="n">
-        <v>1.979770022429321</v>
+        <v>1.969672759100119</v>
       </c>
       <c r="E7" t="n">
-        <v>7.780085138907421</v>
+        <v>7.708204272871346</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747934279368718</v>
+        <v>0.7478683967317376</v>
       </c>
       <c r="G7" t="n">
-        <v>30.1878029162127</v>
+        <v>30.01852178250424</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40497685096103</v>
+        <v>34.40194624965992</v>
       </c>
       <c r="I7" t="n">
-        <v>3.198794791259377</v>
+        <v>3.185839946553122</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674589246054488</v>
+        <v>4.674177479573361</v>
       </c>
       <c r="K7" t="n">
-        <v>17.02604675480695</v>
+        <v>17.29376911300615</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22410039361678</v>
+        <v>42.20776896961728</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89351035252477</v>
+        <v>99.89394151403702</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.60853863855091</v>
+        <v>87.54232202241579</v>
       </c>
       <c r="C8" t="n">
-        <v>42.88363189680243</v>
+        <v>42.69017120181825</v>
       </c>
       <c r="D8" t="n">
-        <v>1.983893849582041</v>
+        <v>1.973873915733266</v>
       </c>
       <c r="E8" t="n">
-        <v>9.562167532822302</v>
+        <v>9.536309595353236</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494922137018817</v>
+        <v>0.7494635410322994</v>
       </c>
       <c r="G8" t="n">
-        <v>30.67740417371164</v>
+        <v>30.52157891759736</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47664183028655</v>
+        <v>34.47532288748577</v>
       </c>
       <c r="I8" t="n">
-        <v>5.474612702809732</v>
+        <v>5.601626033761992</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684326335636761</v>
+        <v>4.684147131451873</v>
       </c>
       <c r="K8" t="n">
-        <v>12.39146136144908</v>
+        <v>12.4576779775842</v>
       </c>
       <c r="L8" t="n">
-        <v>44.54279897901516</v>
+        <v>44.6658273660374</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81789223726669</v>
+        <v>99.81367654543986</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.20828941186601</v>
+        <v>85.33732174951506</v>
       </c>
       <c r="C9" t="n">
-        <v>41.33307141852319</v>
+        <v>41.3542293126157</v>
       </c>
       <c r="D9" t="n">
-        <v>1.874462139218274</v>
+        <v>1.873740336495851</v>
       </c>
       <c r="E9" t="n">
-        <v>9.796440099458129</v>
+        <v>9.831962444244022</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508322358093463</v>
+        <v>0.7508325796894385</v>
       </c>
       <c r="G9" t="n">
-        <v>28.98523661698623</v>
+        <v>28.97323537010137</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53828284722993</v>
+        <v>34.53829866571417</v>
       </c>
       <c r="I9" t="n">
-        <v>4.570333999355684</v>
+        <v>4.676548730211207</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692701473808414</v>
+        <v>4.692703623058992</v>
       </c>
       <c r="K9" t="n">
-        <v>14.79171058813401</v>
+        <v>14.66267825048494</v>
       </c>
       <c r="L9" t="n">
-        <v>43.72314541826476</v>
+        <v>43.8274917137393</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84792742492195</v>
+        <v>99.84439927683995</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.7257628032157</v>
+        <v>82.89596546818603</v>
       </c>
       <c r="C10" t="n">
-        <v>39.55921309384333</v>
+        <v>39.63793510617541</v>
       </c>
       <c r="D10" t="n">
-        <v>1.762709700220746</v>
+        <v>1.764051758472605</v>
       </c>
       <c r="E10" t="n">
-        <v>9.848136232229576</v>
+        <v>9.906940415555969</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519862590712736</v>
+        <v>0.752011036807152</v>
       </c>
       <c r="G10" t="n">
-        <v>27.2571831028088</v>
+        <v>27.27714497455458</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59136791727858</v>
+        <v>34.59250769312899</v>
       </c>
       <c r="I10" t="n">
-        <v>3.814465472411274</v>
+        <v>3.903240609622027</v>
       </c>
       <c r="J10" t="n">
-        <v>4.69991411919546</v>
+        <v>4.700068980044701</v>
       </c>
       <c r="K10" t="n">
-        <v>17.27423719678428</v>
+        <v>17.104034531814</v>
       </c>
       <c r="L10" t="n">
-        <v>43.03959598716808</v>
+        <v>43.12812623061583</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87304627779569</v>
+        <v>99.87009586860523</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.09347958425644</v>
+        <v>80.29798573483252</v>
       </c>
       <c r="C11" t="n">
-        <v>37.51751894653933</v>
+        <v>37.64428520337321</v>
       </c>
       <c r="D11" t="n">
-        <v>1.645509516560368</v>
+        <v>1.648609266294731</v>
       </c>
       <c r="E11" t="n">
-        <v>9.723835641058312</v>
+        <v>9.801463435944079</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529823955594345</v>
+        <v>0.753027821955044</v>
       </c>
       <c r="G11" t="n">
-        <v>25.44488986739194</v>
+        <v>25.49208306793215</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63719019573399</v>
+        <v>34.63927980993202</v>
       </c>
       <c r="I11" t="n">
-        <v>3.182931995705922</v>
+        <v>3.257098445555465</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706139972246466</v>
+        <v>4.706423887219026</v>
       </c>
       <c r="K11" t="n">
-        <v>19.90652041574357</v>
+        <v>19.70201426516748</v>
       </c>
       <c r="L11" t="n">
-        <v>42.47000326348344</v>
+        <v>42.54527718119205</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89404262576635</v>
+        <v>99.89157664973274</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.47318623163335</v>
+        <v>77.66082450874528</v>
       </c>
       <c r="C12" t="n">
-        <v>35.38899795623947</v>
+        <v>35.51039715014372</v>
       </c>
       <c r="D12" t="n">
-        <v>1.530134817815539</v>
+        <v>1.532706871544084</v>
       </c>
       <c r="E12" t="n">
-        <v>9.484629065908557</v>
+        <v>9.565292274873014</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538427039874789</v>
+        <v>0.7539061235234902</v>
       </c>
       <c r="G12" t="n">
-        <v>23.66082452258481</v>
+        <v>23.69990978881657</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67676438342403</v>
+        <v>34.67968168208054</v>
       </c>
       <c r="I12" t="n">
-        <v>2.65547383799119</v>
+        <v>2.717414495885765</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711516899921743</v>
+        <v>4.711913272021815</v>
       </c>
       <c r="K12" t="n">
-        <v>22.52681376836664</v>
+        <v>22.3391754912547</v>
       </c>
       <c r="L12" t="n">
-        <v>41.99577349773539</v>
+        <v>42.0599524017806</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9115852223415</v>
+        <v>99.90952504317903</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.85769880469908</v>
+        <v>75.03720619079584</v>
       </c>
       <c r="C13" t="n">
-        <v>33.18275949419422</v>
+        <v>33.30561542079184</v>
       </c>
       <c r="D13" t="n">
-        <v>1.416116227713518</v>
+        <v>1.418574132493769</v>
       </c>
       <c r="E13" t="n">
-        <v>9.1470578406153</v>
+        <v>9.230813248338961</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545862570131984</v>
+        <v>0.7546652796491884</v>
       </c>
       <c r="G13" t="n">
-        <v>21.89772899576851</v>
+        <v>21.93510030719795</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71096782260712</v>
+        <v>34.71460286386266</v>
       </c>
       <c r="I13" t="n">
-        <v>2.21507755464895</v>
+        <v>2.266792361445884</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71616410633249</v>
+        <v>4.716657997807429</v>
       </c>
       <c r="K13" t="n">
-        <v>25.14230119530092</v>
+        <v>24.96279380920416</v>
       </c>
       <c r="L13" t="n">
-        <v>41.60117614833842</v>
+        <v>41.65610703400716</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92623683783356</v>
+        <v>99.92451626400316</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.43647466616231</v>
+        <v>82.45685574850246</v>
       </c>
       <c r="C14" t="n">
-        <v>37.93118477801575</v>
+        <v>38.00593679215351</v>
       </c>
       <c r="D14" t="n">
-        <v>1.417757785609767</v>
+        <v>1.420197534838852</v>
       </c>
       <c r="E14" t="n">
-        <v>11.75714233919328</v>
+        <v>11.81334616925279</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554609712522983</v>
+        <v>0.7555289112047576</v>
       </c>
       <c r="G14" t="n">
-        <v>24.04479340327841</v>
+        <v>24.06035779872869</v>
       </c>
       <c r="H14" t="n">
-        <v>36.87288530005655</v>
+        <v>36.85448509296916</v>
       </c>
       <c r="I14" t="n">
-        <v>2.866803796445146</v>
+        <v>2.830884546478478</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721631070326864</v>
+        <v>4.722055695029737</v>
       </c>
       <c r="K14" t="n">
-        <v>17.56352533383769</v>
+        <v>17.54314425149753</v>
       </c>
       <c r="L14" t="n">
-        <v>44.40984040636571</v>
+        <v>44.35666400257907</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90455051821915</v>
+        <v>99.90574504623009</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.48482734652771</v>
+        <v>81.46163846575341</v>
       </c>
       <c r="C15" t="n">
-        <v>37.41054789966839</v>
+        <v>37.44688757668762</v>
       </c>
       <c r="D15" t="n">
-        <v>1.381586734312526</v>
+        <v>1.383576444025422</v>
       </c>
       <c r="E15" t="n">
-        <v>11.86687810431671</v>
+        <v>11.90279101209038</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561999898839689</v>
+        <v>0.7562589350310496</v>
       </c>
       <c r="G15" t="n">
-        <v>23.44247939177389</v>
+        <v>23.44044394406401</v>
       </c>
       <c r="H15" t="n">
-        <v>36.92009301840275</v>
+        <v>36.8905998980572</v>
       </c>
       <c r="I15" t="n">
-        <v>2.391340171063081</v>
+        <v>2.361349888541265</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726249936774805</v>
+        <v>4.726618343944062</v>
       </c>
       <c r="K15" t="n">
-        <v>18.5151726534723</v>
+        <v>18.53836153424661</v>
       </c>
       <c r="L15" t="n">
-        <v>43.99464600806917</v>
+        <v>43.93611520721915</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92036656120985</v>
+        <v>99.92136431815337</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.77050111130316</v>
+        <v>78.72125664645814</v>
       </c>
       <c r="C16" t="n">
-        <v>35.06494856437687</v>
+        <v>35.07065377821301</v>
       </c>
       <c r="D16" t="n">
-        <v>1.280459371076074</v>
+        <v>1.281408191320454</v>
       </c>
       <c r="E16" t="n">
-        <v>11.33067463007942</v>
+        <v>11.35208494506536</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756838221489466</v>
+        <v>0.7568895994960332</v>
       </c>
       <c r="G16" t="n">
-        <v>21.72657110332712</v>
+        <v>21.70951739444303</v>
       </c>
       <c r="H16" t="n">
-        <v>36.95125351900769</v>
+        <v>36.9213639517033</v>
       </c>
       <c r="I16" t="n">
-        <v>1.994465382014223</v>
+        <v>1.969432567579759</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730238884309163</v>
+        <v>4.730559996850209</v>
       </c>
       <c r="K16" t="n">
-        <v>21.22949888869683</v>
+        <v>21.27874335354186</v>
       </c>
       <c r="L16" t="n">
-        <v>43.63912643106345</v>
+        <v>43.58500981578565</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93357388413716</v>
+        <v>99.93440694754052</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.64771071407056</v>
+        <v>80.49082743093189</v>
       </c>
       <c r="C17" t="n">
-        <v>36.41335307270759</v>
+        <v>36.35534975981111</v>
       </c>
       <c r="D17" t="n">
-        <v>1.281515077185237</v>
+        <v>1.282445685488797</v>
       </c>
       <c r="E17" t="n">
-        <v>12.16619497224071</v>
+        <v>12.15243304598984</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574622153092799</v>
+        <v>0.757502416357105</v>
       </c>
       <c r="G17" t="n">
-        <v>22.23820268930831</v>
+        <v>22.19240377839569</v>
       </c>
       <c r="H17" t="n">
-        <v>37.47543746752326</v>
+        <v>37.41656663127494</v>
       </c>
       <c r="I17" t="n">
-        <v>1.994759446820745</v>
+        <v>1.955085771193607</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734138845683</v>
+        <v>4.734390102231908</v>
       </c>
       <c r="K17" t="n">
-        <v>19.35228928592947</v>
+        <v>19.50917256906811</v>
       </c>
       <c r="L17" t="n">
-        <v>44.16792043558475</v>
+        <v>44.07036086733748</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93356279422179</v>
+        <v>99.9348831962167</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.01795222608985</v>
+        <v>77.93626099961946</v>
       </c>
       <c r="C18" t="n">
-        <v>34.09066638923237</v>
+        <v>34.10175818536253</v>
       </c>
       <c r="D18" t="n">
-        <v>1.187921634830959</v>
+        <v>1.191321222729482</v>
       </c>
       <c r="E18" t="n">
-        <v>11.55490284667966</v>
+        <v>11.5606682573022</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580005631941023</v>
+        <v>0.7580306310809587</v>
       </c>
       <c r="G18" t="n">
-        <v>20.61407045823378</v>
+        <v>20.61551760338912</v>
       </c>
       <c r="H18" t="n">
-        <v>37.50207222511997</v>
+        <v>37.44265761261562</v>
       </c>
       <c r="I18" t="n">
-        <v>1.663480978068218</v>
+        <v>1.630374228246065</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737503519963139</v>
+        <v>4.737691444255994</v>
       </c>
       <c r="K18" t="n">
-        <v>21.98204777391019</v>
+        <v>22.06373900038056</v>
       </c>
       <c r="L18" t="n">
-        <v>43.87187585222355</v>
+        <v>43.78019487616819</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94459001536609</v>
+        <v>99.94569206191127</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.9743445989984</v>
+        <v>76.88656653676171</v>
       </c>
       <c r="C19" t="n">
-        <v>33.29502269765921</v>
+        <v>33.28147051993279</v>
       </c>
       <c r="D19" t="n">
-        <v>1.151148666902909</v>
+        <v>1.153670597530349</v>
       </c>
       <c r="E19" t="n">
-        <v>11.42956984255891</v>
+        <v>11.42523917979116</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584581883380461</v>
+        <v>0.7584840211610347</v>
       </c>
       <c r="G19" t="n">
-        <v>19.97594709251608</v>
+        <v>19.96398289405776</v>
       </c>
       <c r="H19" t="n">
-        <v>37.52471322571224</v>
+        <v>37.46505265687529</v>
       </c>
       <c r="I19" t="n">
-        <v>1.394143905857436</v>
+        <v>1.379612055089641</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740363677112788</v>
+        <v>4.740525132256469</v>
       </c>
       <c r="K19" t="n">
-        <v>23.02565540100159</v>
+        <v>23.11343346323829</v>
       </c>
       <c r="L19" t="n">
-        <v>43.63287847694387</v>
+        <v>43.55913643747547</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95355657560467</v>
+        <v>99.95404042064655</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.30527693293965</v>
+        <v>74.16220683999975</v>
       </c>
       <c r="C20" t="n">
-        <v>30.83968722229294</v>
+        <v>30.76862978120748</v>
       </c>
       <c r="D20" t="n">
-        <v>1.057325999865678</v>
+        <v>1.057636471761419</v>
       </c>
       <c r="E20" t="n">
-        <v>10.69175174857528</v>
+        <v>10.66588851849809</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588536856121526</v>
+        <v>0.7588761626074904</v>
       </c>
       <c r="G20" t="n">
-        <v>18.34783711271922</v>
+        <v>18.3021362211852</v>
       </c>
       <c r="H20" t="n">
-        <v>37.54428045040648</v>
+        <v>37.4844223463223</v>
       </c>
       <c r="I20" t="n">
-        <v>1.162392400684877</v>
+        <v>1.150271103328425</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742835535075954</v>
+        <v>4.742976016296817</v>
       </c>
       <c r="K20" t="n">
-        <v>25.69472306706035</v>
+        <v>25.83779316000024</v>
       </c>
       <c r="L20" t="n">
-        <v>43.42686349103956</v>
+        <v>43.35525450170647</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96127378039286</v>
+        <v>99.96167744291418</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.88867087060086</v>
+        <v>80.6609741255549</v>
       </c>
       <c r="C21" t="n">
-        <v>34.98762545370242</v>
+        <v>34.91173443567052</v>
       </c>
       <c r="D21" t="n">
-        <v>1.058036459331355</v>
+        <v>1.058307797832247</v>
       </c>
       <c r="E21" t="n">
-        <v>12.90213339754878</v>
+        <v>12.86556421517588</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593635896380402</v>
+        <v>0.7593578530238957</v>
       </c>
       <c r="G21" t="n">
-        <v>20.29160158671629</v>
+        <v>20.25066450656414</v>
       </c>
       <c r="H21" t="n">
-        <v>39.50094377951383</v>
+        <v>39.44512643039739</v>
       </c>
       <c r="I21" t="n">
-        <v>1.630569622614807</v>
+        <v>1.535966741161995</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746022435237751</v>
+        <v>4.74598658139935</v>
       </c>
       <c r="K21" t="n">
-        <v>19.11132912939913</v>
+        <v>19.33902587444509</v>
       </c>
       <c r="L21" t="n">
-        <v>45.84672959311069</v>
+        <v>45.69807327597362</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94568417621224</v>
+        <v>99.94883358608925</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_80_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_80_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.44238459795949</v>
+        <v>45.20216409561898</v>
       </c>
       <c r="M2" t="n">
-        <v>100.548275403597</v>
+        <v>99.65842520250274</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.01057461022427</v>
+        <v>88.05716835626782</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90836689548705</v>
+        <v>45.93399910086031</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228703092105968</v>
+        <v>2.228803158257442</v>
       </c>
       <c r="E3" t="n">
-        <v>5.69387494389947</v>
+        <v>5.7110463737306</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429010307019894</v>
+        <v>0.742934386085814</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9662372889206</v>
+        <v>33.97465036000612</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17344741229151</v>
+        <v>34.17498175994744</v>
       </c>
       <c r="I3" t="n">
-        <v>6.562279400417291</v>
+        <v>6.581412405204056</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643131441887434</v>
+        <v>4.643339913036337</v>
       </c>
       <c r="K3" t="n">
-        <v>11.98942538977574</v>
+        <v>11.94283164373219</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86665262716504</v>
+        <v>48.88693798910404</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7644449124278</v>
+        <v>106.7637687336965</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.0291369579995</v>
+        <v>87.14816229207455</v>
       </c>
       <c r="C4" t="n">
-        <v>42.56170639790567</v>
+        <v>42.66251327016504</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181053791259174</v>
+        <v>2.185050507583856</v>
       </c>
       <c r="E4" t="n">
-        <v>6.485481564339393</v>
+        <v>6.514941973797771</v>
       </c>
       <c r="F4" t="n">
-        <v>0.74446032862147</v>
+        <v>0.7444961696167676</v>
       </c>
       <c r="G4" t="n">
-        <v>33.24004479385656</v>
+        <v>33.30770900026721</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24517511658762</v>
+        <v>34.24682380237131</v>
       </c>
       <c r="I4" t="n">
-        <v>5.480044309451108</v>
+        <v>5.49603977833283</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652877053884188</v>
+        <v>4.653101060104797</v>
       </c>
       <c r="K4" t="n">
-        <v>12.9708630420005</v>
+        <v>12.85183770792546</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28514502119335</v>
+        <v>44.30283201065382</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81771446109951</v>
+        <v>99.81718298874434</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.77547794229123</v>
+        <v>85.91250066764304</v>
       </c>
       <c r="C5" t="n">
-        <v>42.15849872756986</v>
+        <v>42.27987488493591</v>
       </c>
       <c r="D5" t="n">
-        <v>2.119567875725339</v>
+        <v>2.124552343007746</v>
       </c>
       <c r="E5" t="n">
-        <v>7.065120265786818</v>
+        <v>7.0992585113798</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457838513320966</v>
+        <v>0.7458215053521237</v>
       </c>
       <c r="G5" t="n">
-        <v>32.30297731082304</v>
+        <v>32.38550823019005</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30605716127643</v>
+        <v>34.30778924619769</v>
       </c>
       <c r="I5" t="n">
-        <v>4.574822406521896</v>
+        <v>4.58818642306487</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661149070825604</v>
+        <v>4.661384408450773</v>
       </c>
       <c r="K5" t="n">
-        <v>14.22452205770877</v>
+        <v>14.08749933235694</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46475576168106</v>
+        <v>43.4799580110868</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84777654695969</v>
+        <v>99.84733222837966</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.3312150917108</v>
+        <v>84.52225610816737</v>
       </c>
       <c r="C6" t="n">
-        <v>41.42457845399269</v>
+        <v>41.60214414476861</v>
       </c>
       <c r="D6" t="n">
-        <v>2.048869206593518</v>
+        <v>2.056668320954853</v>
       </c>
       <c r="E6" t="n">
-        <v>7.465812486333509</v>
+        <v>7.510632376097139</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469093663297198</v>
+        <v>0.7469478148199549</v>
       </c>
       <c r="G6" t="n">
-        <v>31.2255041470589</v>
+        <v>31.35072150811758</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35783085116711</v>
+        <v>34.35959948171793</v>
       </c>
       <c r="I6" t="n">
-        <v>3.818105494667313</v>
+        <v>3.829262763835207</v>
       </c>
       <c r="J6" t="n">
-        <v>4.66818353956075</v>
+        <v>4.668423842624718</v>
       </c>
       <c r="K6" t="n">
-        <v>15.66878490828919</v>
+        <v>15.47774389183262</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77955823753695</v>
+        <v>42.79266234053586</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87292159981882</v>
+        <v>99.87255037713707</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.70623088699385</v>
+        <v>82.91983865357021</v>
       </c>
       <c r="C7" t="n">
-        <v>40.39240343141359</v>
+        <v>40.59439461592504</v>
       </c>
       <c r="D7" t="n">
-        <v>1.969672759100119</v>
+        <v>1.978663988948635</v>
       </c>
       <c r="E7" t="n">
-        <v>7.708204272871346</v>
+        <v>7.758297871383714</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478683967317376</v>
+        <v>0.7479072197484208</v>
       </c>
       <c r="G7" t="n">
-        <v>30.01852178250424</v>
+        <v>30.16166634339451</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40194624965992</v>
+        <v>34.40373210842736</v>
       </c>
       <c r="I7" t="n">
-        <v>3.185839946553122</v>
+        <v>3.195150998239938</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674177479573361</v>
+        <v>4.674420123427629</v>
       </c>
       <c r="K7" t="n">
-        <v>17.29376911300615</v>
+        <v>17.08016134642977</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20776896961728</v>
+        <v>42.21907562753866</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89394151403702</v>
+        <v>99.89363158989347</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.54232202241579</v>
+        <v>87.72150126202831</v>
       </c>
       <c r="C8" t="n">
-        <v>42.69017120181825</v>
+        <v>42.84303298041438</v>
       </c>
       <c r="D8" t="n">
-        <v>1.973873915733266</v>
+        <v>1.982893432989688</v>
       </c>
       <c r="E8" t="n">
-        <v>9.536309595353236</v>
+        <v>9.554854704016753</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494635410322994</v>
+        <v>0.749505890240982</v>
       </c>
       <c r="G8" t="n">
-        <v>30.52157891759736</v>
+        <v>30.64735701369251</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47532288748577</v>
+        <v>34.47727095108517</v>
       </c>
       <c r="I8" t="n">
-        <v>5.601626033761992</v>
+        <v>5.625207455997073</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684147131451873</v>
+        <v>4.684411814006137</v>
       </c>
       <c r="K8" t="n">
-        <v>12.4576779775842</v>
+        <v>12.27849873797169</v>
       </c>
       <c r="L8" t="n">
-        <v>44.6658273660374</v>
+        <v>44.69136131226685</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81367654543986</v>
+        <v>99.81289303065292</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.33732174951506</v>
+        <v>85.65629271321498</v>
       </c>
       <c r="C9" t="n">
-        <v>41.3542293126157</v>
+        <v>41.65068130545952</v>
       </c>
       <c r="D9" t="n">
-        <v>1.873740336495851</v>
+        <v>1.889265591235725</v>
       </c>
       <c r="E9" t="n">
-        <v>9.831962444244022</v>
+        <v>9.886402241173815</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508325796894385</v>
+        <v>0.7508756512221432</v>
       </c>
       <c r="G9" t="n">
-        <v>28.97323537010137</v>
+        <v>29.20025660732885</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53829866571417</v>
+        <v>34.54027995621859</v>
       </c>
       <c r="I9" t="n">
-        <v>4.676548730211207</v>
+        <v>4.69623984589746</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692703623058992</v>
+        <v>4.692972820138395</v>
       </c>
       <c r="K9" t="n">
-        <v>14.66267825048494</v>
+        <v>14.34370728678502</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8274917137393</v>
+        <v>43.84935564508888</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84439927683995</v>
+        <v>99.84374423733342</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.89596546818603</v>
+        <v>83.30356173320277</v>
       </c>
       <c r="C10" t="n">
-        <v>39.63793510617541</v>
+        <v>40.02632464510075</v>
       </c>
       <c r="D10" t="n">
-        <v>1.764051758472605</v>
+        <v>1.783581916685704</v>
       </c>
       <c r="E10" t="n">
-        <v>9.906940415555969</v>
+        <v>9.986645092685189</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752011036807152</v>
+        <v>0.7520533462615172</v>
       </c>
       <c r="G10" t="n">
-        <v>27.27714497455458</v>
+        <v>27.56682273208023</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59250769312899</v>
+        <v>34.5944539280298</v>
       </c>
       <c r="I10" t="n">
-        <v>3.903240609622027</v>
+        <v>3.919671303325854</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700068980044701</v>
+        <v>4.700333414134483</v>
       </c>
       <c r="K10" t="n">
-        <v>17.104034531814</v>
+        <v>16.69643826679723</v>
       </c>
       <c r="L10" t="n">
-        <v>43.12812623061583</v>
+        <v>43.14678598127153</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87009586860523</v>
+        <v>99.86954889316951</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.29798573483252</v>
+        <v>80.8658124980077</v>
       </c>
       <c r="C11" t="n">
-        <v>37.64428520337321</v>
+        <v>38.19575264464616</v>
       </c>
       <c r="D11" t="n">
-        <v>1.648609266294731</v>
+        <v>1.675307558605371</v>
       </c>
       <c r="E11" t="n">
-        <v>9.801463435944079</v>
+        <v>9.925527276664599</v>
       </c>
       <c r="F11" t="n">
-        <v>0.753027821955044</v>
+        <v>0.7530672949577641</v>
       </c>
       <c r="G11" t="n">
-        <v>25.49208306793215</v>
+        <v>25.89334757082903</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63927980993202</v>
+        <v>34.64109556805716</v>
       </c>
       <c r="I11" t="n">
-        <v>3.257098445555465</v>
+        <v>3.270796635407753</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706423887219026</v>
+        <v>4.706670593486026</v>
       </c>
       <c r="K11" t="n">
-        <v>19.70201426516748</v>
+        <v>19.13418750199229</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54527718119205</v>
+        <v>42.56118009493583</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89157664973274</v>
+        <v>99.8911202415743</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.66082450874528</v>
+        <v>78.3419700327066</v>
       </c>
       <c r="C12" t="n">
-        <v>35.51039715014372</v>
+        <v>36.17768454622895</v>
       </c>
       <c r="D12" t="n">
-        <v>1.532706871544084</v>
+        <v>1.564351958878269</v>
       </c>
       <c r="E12" t="n">
-        <v>9.565292274873014</v>
+        <v>9.722964483695637</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539061235234902</v>
+        <v>0.7539416630411738</v>
       </c>
       <c r="G12" t="n">
-        <v>23.69990978881657</v>
+        <v>24.17843146846554</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67968168208054</v>
+        <v>34.681316499894</v>
       </c>
       <c r="I12" t="n">
-        <v>2.717414495885765</v>
+        <v>2.728828564724642</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711913272021815</v>
+        <v>4.712135394007337</v>
       </c>
       <c r="K12" t="n">
-        <v>22.3391754912547</v>
+        <v>21.65802996729341</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0599524017806</v>
+        <v>42.07343002438298</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90952504317903</v>
+        <v>99.90914453790533</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.03720619079584</v>
+        <v>75.95475557373064</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30561542079184</v>
+        <v>34.21147908242754</v>
       </c>
       <c r="D13" t="n">
-        <v>1.418574132493769</v>
+        <v>1.460512320172615</v>
       </c>
       <c r="E13" t="n">
-        <v>9.230813248338961</v>
+        <v>9.456949388307713</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546652796491884</v>
+        <v>0.7546948280847621</v>
       </c>
       <c r="G13" t="n">
-        <v>21.93510030719795</v>
+        <v>22.57349878441969</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71460286386266</v>
+        <v>34.71596209189907</v>
       </c>
       <c r="I13" t="n">
-        <v>2.266792361445884</v>
+        <v>2.276295485317038</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716657997807429</v>
+        <v>4.716842675529763</v>
       </c>
       <c r="K13" t="n">
-        <v>24.96279380920416</v>
+        <v>24.04524442626935</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65610703400716</v>
+        <v>41.66747569783854</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92451626400316</v>
+        <v>99.92419920653543</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.45685574850246</v>
+        <v>83.1316796679706</v>
       </c>
       <c r="C14" t="n">
-        <v>38.00593679215351</v>
+        <v>38.59253059914165</v>
       </c>
       <c r="D14" t="n">
-        <v>1.420197534838852</v>
+        <v>1.462322534505263</v>
       </c>
       <c r="E14" t="n">
-        <v>11.81334616925279</v>
+        <v>11.90239355748129</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555289112047576</v>
+        <v>0.7556302254625896</v>
       </c>
       <c r="G14" t="n">
-        <v>24.06035779872869</v>
+        <v>24.5200173270279</v>
       </c>
       <c r="H14" t="n">
-        <v>36.85448509296916</v>
+        <v>36.67753046380981</v>
       </c>
       <c r="I14" t="n">
-        <v>2.830884546478478</v>
+        <v>3.091096650542561</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722055695029737</v>
+        <v>4.722688909141185</v>
       </c>
       <c r="K14" t="n">
-        <v>17.54314425149753</v>
+        <v>16.8683203320294</v>
       </c>
       <c r="L14" t="n">
-        <v>44.35666400257907</v>
+        <v>44.43624006313345</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90574504623009</v>
+        <v>99.89709099430451</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.46163846575341</v>
+        <v>82.3572770788607</v>
       </c>
       <c r="C15" t="n">
-        <v>37.44688757668762</v>
+        <v>38.29528003460918</v>
       </c>
       <c r="D15" t="n">
-        <v>1.383576444025422</v>
+        <v>1.433926148801209</v>
       </c>
       <c r="E15" t="n">
-        <v>11.90279101209038</v>
+        <v>12.10103172967688</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562589350310496</v>
+        <v>0.7564188502938274</v>
       </c>
       <c r="G15" t="n">
-        <v>23.44044394406401</v>
+        <v>24.04387074988174</v>
       </c>
       <c r="H15" t="n">
-        <v>36.8905998980572</v>
+        <v>36.71580951922283</v>
       </c>
       <c r="I15" t="n">
-        <v>2.361349888541265</v>
+        <v>2.578602266647799</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726618343944062</v>
+        <v>4.727617814336421</v>
       </c>
       <c r="K15" t="n">
-        <v>18.53836153424661</v>
+        <v>17.64272292113928</v>
       </c>
       <c r="L15" t="n">
-        <v>43.93611520721915</v>
+        <v>43.97613324840313</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92136431815337</v>
+        <v>99.91413620415159</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.72125664645814</v>
+        <v>79.85090464234973</v>
       </c>
       <c r="C16" t="n">
-        <v>35.07065377821301</v>
+        <v>36.18701424584376</v>
       </c>
       <c r="D16" t="n">
-        <v>1.281408191320454</v>
+        <v>1.339489991518692</v>
       </c>
       <c r="E16" t="n">
-        <v>11.35208494506536</v>
+        <v>11.66253725535087</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568895994960332</v>
+        <v>0.757097982157563</v>
       </c>
       <c r="G16" t="n">
-        <v>21.70951739444303</v>
+        <v>22.46037862811897</v>
       </c>
       <c r="H16" t="n">
-        <v>36.9213639517033</v>
+        <v>36.74877389621801</v>
       </c>
       <c r="I16" t="n">
-        <v>1.969432567579759</v>
+        <v>2.15076450050086</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730559996850209</v>
+        <v>4.731862388484768</v>
       </c>
       <c r="K16" t="n">
-        <v>21.27874335354186</v>
+        <v>20.14909535765026</v>
       </c>
       <c r="L16" t="n">
-        <v>43.58500981578565</v>
+        <v>43.59226255576575</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93440694754052</v>
+        <v>99.92837215925978</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.49082743093189</v>
+        <v>81.58367952286831</v>
       </c>
       <c r="C17" t="n">
-        <v>36.35534975981111</v>
+        <v>37.43223398839771</v>
       </c>
       <c r="D17" t="n">
-        <v>1.282445685488797</v>
+        <v>1.340680356776783</v>
       </c>
       <c r="E17" t="n">
-        <v>12.15243304598984</v>
+        <v>12.46105785855868</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757502416357105</v>
+        <v>0.7577707928098544</v>
       </c>
       <c r="G17" t="n">
-        <v>22.19240377839569</v>
+        <v>22.90598990283835</v>
       </c>
       <c r="H17" t="n">
-        <v>37.41656663127494</v>
+        <v>37.20708284649206</v>
       </c>
       <c r="I17" t="n">
-        <v>1.955085771193607</v>
+        <v>2.175030310331003</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734390102231908</v>
+        <v>4.73606745506159</v>
       </c>
       <c r="K17" t="n">
-        <v>19.50917256906811</v>
+        <v>18.41632047713168</v>
       </c>
       <c r="L17" t="n">
-        <v>44.07036086733748</v>
+        <v>44.07900889643053</v>
       </c>
       <c r="M17" t="n">
-        <v>99.9348831962167</v>
+        <v>99.92756336195993</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>77.93626099961946</v>
+        <v>79.13764530026036</v>
       </c>
       <c r="C18" t="n">
-        <v>34.10175818536253</v>
+        <v>35.32155223147723</v>
       </c>
       <c r="D18" t="n">
-        <v>1.191321222729482</v>
+        <v>1.25229964830364</v>
       </c>
       <c r="E18" t="n">
-        <v>11.5606682573022</v>
+        <v>11.94191483667492</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580306310809587</v>
+        <v>0.758349753715356</v>
       </c>
       <c r="G18" t="n">
-        <v>20.61551760338912</v>
+        <v>21.39597477830962</v>
       </c>
       <c r="H18" t="n">
-        <v>37.44265761261562</v>
+        <v>37.23551023717572</v>
       </c>
       <c r="I18" t="n">
-        <v>1.630374228246065</v>
+        <v>1.813910085360116</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737691444255994</v>
+        <v>4.739685960720974</v>
       </c>
       <c r="K18" t="n">
-        <v>22.06373900038056</v>
+        <v>20.86235469973965</v>
       </c>
       <c r="L18" t="n">
-        <v>43.78019487616819</v>
+        <v>43.75567556016281</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94569206191127</v>
+        <v>99.9395824913797</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.88656653676171</v>
+        <v>78.14587395195318</v>
       </c>
       <c r="C19" t="n">
-        <v>33.28147051993279</v>
+        <v>34.60869962499638</v>
       </c>
       <c r="D19" t="n">
-        <v>1.153670597530349</v>
+        <v>1.217178465050057</v>
       </c>
       <c r="E19" t="n">
-        <v>11.42523917979116</v>
+        <v>11.85909414306028</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584840211610347</v>
+        <v>0.7588390330398871</v>
       </c>
       <c r="G19" t="n">
-        <v>19.96398289405776</v>
+        <v>20.79591715464427</v>
       </c>
       <c r="H19" t="n">
-        <v>37.46505265687529</v>
+        <v>37.25953419868974</v>
       </c>
       <c r="I19" t="n">
-        <v>1.379612055089641</v>
+        <v>1.512567000969649</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740525132256469</v>
+        <v>4.742743956499294</v>
       </c>
       <c r="K19" t="n">
-        <v>23.11343346323829</v>
+        <v>21.85412604804682</v>
       </c>
       <c r="L19" t="n">
-        <v>43.55913643747547</v>
+        <v>43.4867879356968</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95404042064655</v>
+        <v>99.94961360873999</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.16220683999975</v>
+        <v>75.48867561563875</v>
       </c>
       <c r="C20" t="n">
-        <v>30.76862978120748</v>
+        <v>32.18390920961475</v>
       </c>
       <c r="D20" t="n">
-        <v>1.057636471761419</v>
+        <v>1.122318171531752</v>
       </c>
       <c r="E20" t="n">
-        <v>10.66588851849809</v>
+        <v>11.14505635312951</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588761626074904</v>
+        <v>0.7592616255201861</v>
       </c>
       <c r="G20" t="n">
-        <v>18.3021362211852</v>
+        <v>19.17519606737891</v>
       </c>
       <c r="H20" t="n">
-        <v>37.4844223463223</v>
+        <v>37.2802837889009</v>
       </c>
       <c r="I20" t="n">
-        <v>1.150271103328425</v>
+        <v>1.261174449676342</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742976016296817</v>
+        <v>4.745385159501163</v>
       </c>
       <c r="K20" t="n">
-        <v>25.83779316000024</v>
+        <v>24.51132438436124</v>
       </c>
       <c r="L20" t="n">
-        <v>43.35525450170647</v>
+        <v>43.26275065599707</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96167744291418</v>
+        <v>99.95798424997307</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.6609741255549</v>
+        <v>81.48224535006554</v>
       </c>
       <c r="C21" t="n">
-        <v>34.91173443567052</v>
+        <v>35.86380238877432</v>
       </c>
       <c r="D21" t="n">
-        <v>1.058307797832247</v>
+        <v>1.123170273618322</v>
       </c>
       <c r="E21" t="n">
-        <v>12.86556421517588</v>
+        <v>13.14055351282711</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593578530238957</v>
+        <v>0.7598380827421832</v>
       </c>
       <c r="G21" t="n">
-        <v>20.25066450656414</v>
+        <v>20.86746953683241</v>
       </c>
       <c r="H21" t="n">
-        <v>39.44512643039739</v>
+        <v>38.98630325607265</v>
       </c>
       <c r="I21" t="n">
-        <v>1.535966741161995</v>
+        <v>1.855922670834232</v>
       </c>
       <c r="J21" t="n">
-        <v>4.74598658139935</v>
+        <v>4.748988017138646</v>
       </c>
       <c r="K21" t="n">
-        <v>19.33902587444509</v>
+        <v>18.51775464993447</v>
       </c>
       <c r="L21" t="n">
-        <v>45.69807327597362</v>
+        <v>45.55662580594798</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94883358608925</v>
+        <v>99.93818284465675</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_80_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_80_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.20216409561898</v>
+        <v>43.52008901601063</v>
       </c>
       <c r="M2" t="n">
-        <v>99.65842520250274</v>
+        <v>97.68722906053017</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.05716835626782</v>
+        <v>81.57470203507701</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93399910086031</v>
+        <v>43.33025759063256</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228803158257442</v>
+        <v>2.185751904011397</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7110463737306</v>
+        <v>4.155212845932895</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742934386085814</v>
+        <v>0.7377019285160163</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97465036000612</v>
+        <v>32.87735155617143</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17498175994744</v>
+        <v>33.93428871173675</v>
       </c>
       <c r="I3" t="n">
-        <v>6.581412405204056</v>
+        <v>3.073758035483401</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643339913036337</v>
+        <v>4.610637053225101</v>
       </c>
       <c r="K3" t="n">
-        <v>11.94283164373219</v>
+        <v>18.425297964923</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88693798910404</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7637687336965</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.14816229207455</v>
+        <v>88.67164177317771</v>
       </c>
       <c r="C4" t="n">
-        <v>42.66251327016504</v>
+        <v>42.92297566207665</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185050507583856</v>
+        <v>2.191495079768461</v>
       </c>
       <c r="E4" t="n">
-        <v>6.514941973797771</v>
+        <v>6.537615235622553</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444961696167676</v>
+        <v>0.7396402783461214</v>
       </c>
       <c r="G4" t="n">
-        <v>33.30770900026721</v>
+        <v>33.56700739866303</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24682380237131</v>
+        <v>34.02345280392159</v>
       </c>
       <c r="I4" t="n">
-        <v>5.49603977833283</v>
+        <v>6.989679237192704</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653101060104797</v>
+        <v>4.622751739663259</v>
       </c>
       <c r="K4" t="n">
-        <v>12.85183770792546</v>
+        <v>11.32835822682228</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30283201065382</v>
+        <v>45.51628739025787</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81718298874434</v>
+        <v>99.7676212791568</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.91250066764304</v>
+        <v>87.52517371326931</v>
       </c>
       <c r="C5" t="n">
-        <v>42.27987488493591</v>
+        <v>42.86007871543517</v>
       </c>
       <c r="D5" t="n">
-        <v>2.124552343007746</v>
+        <v>2.136833111625213</v>
       </c>
       <c r="E5" t="n">
-        <v>7.0992585113798</v>
+        <v>7.347496050216415</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458215053521237</v>
+        <v>0.7412846757638448</v>
       </c>
       <c r="G5" t="n">
-        <v>32.38550823019005</v>
+        <v>32.72975309404296</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30778924619769</v>
+        <v>34.09909508513686</v>
       </c>
       <c r="I5" t="n">
-        <v>4.58818642306487</v>
+        <v>5.837682472959979</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661384408450773</v>
+        <v>4.633029223524029</v>
       </c>
       <c r="K5" t="n">
-        <v>14.08749933235694</v>
+        <v>12.47482628673071</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4799580110868</v>
+        <v>44.47093724124543</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84733222837966</v>
+        <v>99.80584224341131</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.52225610816737</v>
+        <v>86.05564637990391</v>
       </c>
       <c r="C6" t="n">
-        <v>41.60214414476861</v>
+        <v>42.29662883063861</v>
       </c>
       <c r="D6" t="n">
-        <v>2.056668320954853</v>
+        <v>2.066340843079971</v>
       </c>
       <c r="E6" t="n">
-        <v>7.510632376097139</v>
+        <v>7.917428453614838</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469478148199549</v>
+        <v>0.7426841430424046</v>
       </c>
       <c r="G6" t="n">
-        <v>31.35072150811758</v>
+        <v>31.65002696476655</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35959948171793</v>
+        <v>34.16347057995061</v>
       </c>
       <c r="I6" t="n">
-        <v>3.829262763835207</v>
+        <v>4.873919501434504</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668423842624718</v>
+        <v>4.641775894015028</v>
       </c>
       <c r="K6" t="n">
-        <v>15.47774389183262</v>
+        <v>13.94435362009608</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79266234053586</v>
+        <v>43.5968597027942</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87255037713707</v>
+        <v>99.8378421535289</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.91983865357021</v>
+        <v>84.38062841151405</v>
       </c>
       <c r="C7" t="n">
-        <v>40.59439461592504</v>
+        <v>41.37839570020204</v>
       </c>
       <c r="D7" t="n">
-        <v>1.978663988948635</v>
+        <v>1.986394588524695</v>
       </c>
       <c r="E7" t="n">
-        <v>7.758297871383714</v>
+        <v>8.289126090208795</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479072197484208</v>
+        <v>0.74387767656582</v>
       </c>
       <c r="G7" t="n">
-        <v>30.16166634339451</v>
+        <v>30.4254946612599</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40373210842736</v>
+        <v>34.21837312202772</v>
       </c>
       <c r="I7" t="n">
-        <v>3.195150998239938</v>
+        <v>4.068126794390763</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674420123427629</v>
+        <v>4.649235478536374</v>
       </c>
       <c r="K7" t="n">
-        <v>17.08016134642977</v>
+        <v>15.61937158848593</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21907562753866</v>
+        <v>42.86684605849439</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89363158989347</v>
+        <v>99.86461334718237</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.72150126202831</v>
+        <v>82.42212788283207</v>
       </c>
       <c r="C8" t="n">
-        <v>42.84303298041438</v>
+        <v>40.05141009820925</v>
       </c>
       <c r="D8" t="n">
-        <v>1.982893432989688</v>
+        <v>1.893406783421704</v>
       </c>
       <c r="E8" t="n">
-        <v>9.554854704016753</v>
+        <v>8.466885923934168</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749505890240982</v>
+        <v>0.7448989582049016</v>
       </c>
       <c r="G8" t="n">
-        <v>30.64735701369251</v>
+        <v>29.0012056584266</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47727095108517</v>
+        <v>34.26535207742547</v>
       </c>
       <c r="I8" t="n">
-        <v>5.625207455997073</v>
+        <v>3.394759992638603</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684411814006137</v>
+        <v>4.655618488780633</v>
       </c>
       <c r="K8" t="n">
-        <v>12.27849873797169</v>
+        <v>17.57787211716793</v>
       </c>
       <c r="L8" t="n">
-        <v>44.69136131226685</v>
+        <v>42.2577142625564</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81289303065292</v>
+        <v>99.88699647793358</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.65629271321498</v>
+        <v>80.37929408107787</v>
       </c>
       <c r="C9" t="n">
-        <v>41.65068130545952</v>
+        <v>38.53505796565518</v>
       </c>
       <c r="D9" t="n">
-        <v>1.889265591235725</v>
+        <v>1.797248801846019</v>
       </c>
       <c r="E9" t="n">
-        <v>9.886402241173815</v>
+        <v>8.508937466221184</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508756512221432</v>
+        <v>0.7457738806455465</v>
       </c>
       <c r="G9" t="n">
-        <v>29.20025660732885</v>
+        <v>27.52835924011177</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54027995621859</v>
+        <v>34.30559850969514</v>
       </c>
       <c r="I9" t="n">
-        <v>4.69623984589746</v>
+        <v>2.83228942852355</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692972820138395</v>
+        <v>4.661086754034664</v>
       </c>
       <c r="K9" t="n">
-        <v>14.34370728678502</v>
+        <v>19.62070591892214</v>
       </c>
       <c r="L9" t="n">
-        <v>43.84935564508888</v>
+        <v>41.74993722673827</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84374423733342</v>
+        <v>99.90570111131559</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.30356173320277</v>
+        <v>85.5136155829683</v>
       </c>
       <c r="C10" t="n">
-        <v>40.02632464510075</v>
+        <v>41.98760834965401</v>
       </c>
       <c r="D10" t="n">
-        <v>1.783581916685704</v>
+        <v>1.799357169805395</v>
       </c>
       <c r="E10" t="n">
-        <v>9.986645092685189</v>
+        <v>10.47535430071273</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520533462615172</v>
+        <v>0.7466487543710306</v>
       </c>
       <c r="G10" t="n">
-        <v>27.56682273208023</v>
+        <v>29.01550414766182</v>
       </c>
       <c r="H10" t="n">
-        <v>34.5944539280298</v>
+        <v>35.80069385466617</v>
       </c>
       <c r="I10" t="n">
-        <v>3.919671303325854</v>
+        <v>3.009502640932209</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700333414134483</v>
+        <v>4.66655471481894</v>
       </c>
       <c r="K10" t="n">
-        <v>16.69643826679723</v>
+        <v>14.4863844170317</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14678598127153</v>
+        <v>43.42580802316799</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86954889316951</v>
+        <v>99.8998007898537</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.8658124980077</v>
+        <v>85.05854606961876</v>
       </c>
       <c r="C11" t="n">
-        <v>38.19575264464616</v>
+        <v>41.90857179393795</v>
       </c>
       <c r="D11" t="n">
-        <v>1.675307558605371</v>
+        <v>1.77309107473184</v>
       </c>
       <c r="E11" t="n">
-        <v>9.925527276664599</v>
+        <v>10.79321658378309</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530672949577641</v>
+        <v>0.7473964544217664</v>
       </c>
       <c r="G11" t="n">
-        <v>25.89334757082903</v>
+        <v>28.63683526090164</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64109556805716</v>
+        <v>35.88142954958374</v>
       </c>
       <c r="I11" t="n">
-        <v>3.270796635407753</v>
+        <v>2.55534930606065</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706670593486026</v>
+        <v>4.671227840136038</v>
       </c>
       <c r="K11" t="n">
-        <v>19.13418750199229</v>
+        <v>14.94145393038123</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56118009493583</v>
+        <v>43.06488117838887</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8911202415743</v>
+        <v>99.91490690270805</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.3419700327066</v>
+        <v>82.98563487948682</v>
       </c>
       <c r="C12" t="n">
-        <v>36.17768454622895</v>
+        <v>40.23253780954817</v>
       </c>
       <c r="D12" t="n">
-        <v>1.564351958878269</v>
+        <v>1.685329227033179</v>
       </c>
       <c r="E12" t="n">
-        <v>9.722964483695637</v>
+        <v>10.6142033216499</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539416630411738</v>
+        <v>0.7480362887249755</v>
       </c>
       <c r="G12" t="n">
-        <v>24.17843146846554</v>
+        <v>27.21941141248541</v>
       </c>
       <c r="H12" t="n">
-        <v>34.681316499894</v>
+        <v>35.91214707485186</v>
       </c>
       <c r="I12" t="n">
-        <v>2.728828564724642</v>
+        <v>2.131280750210413</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712135394007337</v>
+        <v>4.675226804531095</v>
       </c>
       <c r="K12" t="n">
-        <v>21.65802996729341</v>
+        <v>17.01436512051315</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07343002438298</v>
+        <v>42.68211514477032</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90914453790533</v>
+        <v>99.92901807483165</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.95475557373064</v>
+        <v>84.14281108100552</v>
       </c>
       <c r="C13" t="n">
-        <v>34.21147908242754</v>
+        <v>41.1943152347242</v>
       </c>
       <c r="D13" t="n">
-        <v>1.460512320172615</v>
+        <v>1.686663786739336</v>
       </c>
       <c r="E13" t="n">
-        <v>9.456949388307713</v>
+        <v>11.25321821109426</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546948280847621</v>
+        <v>0.7486286353559261</v>
       </c>
       <c r="G13" t="n">
-        <v>22.57349878441969</v>
+        <v>27.53842509630399</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71596209189907</v>
+        <v>36.23804426520743</v>
       </c>
       <c r="I13" t="n">
-        <v>2.276295485317038</v>
+        <v>1.998902115330042</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716842675529763</v>
+        <v>4.678928970974536</v>
       </c>
       <c r="K13" t="n">
-        <v>24.04524442626935</v>
+        <v>15.85718891899448</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66747569783854</v>
+        <v>42.88191849629944</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92419920653543</v>
+        <v>99.93342265001813</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.1316796679706</v>
+        <v>82.02137210185266</v>
       </c>
       <c r="C14" t="n">
-        <v>38.59253059914165</v>
+        <v>39.3831220441365</v>
       </c>
       <c r="D14" t="n">
-        <v>1.462322534505263</v>
+        <v>1.599349643257024</v>
       </c>
       <c r="E14" t="n">
-        <v>11.90239355748129</v>
+        <v>10.94848209439584</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556302254625896</v>
+        <v>0.7491357691252517</v>
       </c>
       <c r="G14" t="n">
-        <v>24.5200173270279</v>
+        <v>26.11283333400975</v>
       </c>
       <c r="H14" t="n">
-        <v>36.67753046380981</v>
+        <v>36.26259253268383</v>
       </c>
       <c r="I14" t="n">
-        <v>3.091096650542561</v>
+        <v>1.666880171348153</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722688909141185</v>
+        <v>4.682098557032822</v>
       </c>
       <c r="K14" t="n">
-        <v>16.8683203320294</v>
+        <v>17.97862789814733</v>
       </c>
       <c r="L14" t="n">
-        <v>44.43624006313345</v>
+        <v>42.582724998957</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89709099430451</v>
+        <v>99.94447494124083</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.3572770788607</v>
+        <v>81.02331756823833</v>
       </c>
       <c r="C15" t="n">
-        <v>38.29528003460918</v>
+        <v>38.61776881731148</v>
       </c>
       <c r="D15" t="n">
-        <v>1.433926148801209</v>
+        <v>1.557742713945395</v>
       </c>
       <c r="E15" t="n">
-        <v>12.10103172967688</v>
+        <v>10.89941769566208</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564188502938274</v>
+        <v>0.7495717318786618</v>
       </c>
       <c r="G15" t="n">
-        <v>24.04387074988174</v>
+        <v>25.43351045096467</v>
       </c>
       <c r="H15" t="n">
-        <v>36.71580951922283</v>
+        <v>36.28369570294734</v>
       </c>
       <c r="I15" t="n">
-        <v>2.578602266647799</v>
+        <v>1.414555948598541</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727617814336421</v>
+        <v>4.684823324241635</v>
       </c>
       <c r="K15" t="n">
-        <v>17.64272292113928</v>
+        <v>18.97668243176168</v>
       </c>
       <c r="L15" t="n">
-        <v>43.97613324840313</v>
+        <v>42.35842431024265</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91413620415159</v>
+        <v>99.9528755593158</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.85090464234973</v>
+        <v>78.46793628633135</v>
       </c>
       <c r="C16" t="n">
-        <v>36.18701424584376</v>
+        <v>36.28132741451584</v>
       </c>
       <c r="D16" t="n">
-        <v>1.339489991518692</v>
+        <v>1.453414934443584</v>
       </c>
       <c r="E16" t="n">
-        <v>11.66253725535087</v>
+        <v>10.36600799525917</v>
       </c>
       <c r="F16" t="n">
-        <v>0.757097982157563</v>
+        <v>0.7499472718142098</v>
       </c>
       <c r="G16" t="n">
-        <v>22.46037862811897</v>
+        <v>23.73013437574313</v>
       </c>
       <c r="H16" t="n">
-        <v>36.74877389621801</v>
+        <v>36.3018740522183</v>
       </c>
       <c r="I16" t="n">
-        <v>2.15076450050086</v>
+        <v>1.179387208014139</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731862388484768</v>
+        <v>4.687170448838811</v>
       </c>
       <c r="K16" t="n">
-        <v>20.14909535765026</v>
+        <v>21.53206371366866</v>
       </c>
       <c r="L16" t="n">
-        <v>43.59226255576575</v>
+        <v>42.1473156510211</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92837215925978</v>
+        <v>99.96070677920559</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.58367952286831</v>
+        <v>83.51177310914682</v>
       </c>
       <c r="C17" t="n">
-        <v>37.43223398839771</v>
+        <v>39.57958173644821</v>
       </c>
       <c r="D17" t="n">
-        <v>1.340680356776783</v>
+        <v>1.454211122036321</v>
       </c>
       <c r="E17" t="n">
-        <v>12.46105785855868</v>
+        <v>12.12699390733705</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577707928098544</v>
+        <v>0.7503580964857302</v>
       </c>
       <c r="G17" t="n">
-        <v>22.90598990283835</v>
+        <v>25.26970049313861</v>
       </c>
       <c r="H17" t="n">
-        <v>37.20708284649206</v>
+        <v>37.84832702821989</v>
       </c>
       <c r="I17" t="n">
-        <v>2.175030310331003</v>
+        <v>1.372444358893409</v>
       </c>
       <c r="J17" t="n">
-        <v>4.73606745506159</v>
+        <v>4.689738103035813</v>
       </c>
       <c r="K17" t="n">
-        <v>18.41632047713168</v>
+        <v>16.4882268908532</v>
       </c>
       <c r="L17" t="n">
-        <v>44.07900889643053</v>
+        <v>43.88646827473201</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92756336195993</v>
+        <v>99.95427690203341</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.13764530026036</v>
+        <v>85.0697674458783</v>
       </c>
       <c r="C18" t="n">
-        <v>35.32155223147723</v>
+        <v>40.33267831837369</v>
       </c>
       <c r="D18" t="n">
-        <v>1.25229964830364</v>
+        <v>1.455424742198097</v>
       </c>
       <c r="E18" t="n">
-        <v>11.94191483667492</v>
+        <v>12.74345705985031</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758349753715356</v>
+        <v>0.7509843121023262</v>
       </c>
       <c r="G18" t="n">
-        <v>21.39597477830962</v>
+        <v>25.41647207027944</v>
       </c>
       <c r="H18" t="n">
-        <v>37.23551023717572</v>
+        <v>37.87991356477905</v>
       </c>
       <c r="I18" t="n">
-        <v>1.813910085360116</v>
+        <v>2.129863746029547</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739685960720974</v>
+        <v>4.693651950639538</v>
       </c>
       <c r="K18" t="n">
-        <v>20.86235469973965</v>
+        <v>14.93023255412169</v>
       </c>
       <c r="L18" t="n">
-        <v>43.75567556016281</v>
+        <v>44.66615286956114</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9395824913797</v>
+        <v>99.92906374205651</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.14587395195318</v>
+        <v>82.16009305246273</v>
       </c>
       <c r="C19" t="n">
-        <v>34.60869962499638</v>
+        <v>37.75247820018538</v>
       </c>
       <c r="D19" t="n">
-        <v>1.217178465050057</v>
+        <v>1.349498253445414</v>
       </c>
       <c r="E19" t="n">
-        <v>11.85909414306028</v>
+        <v>12.11200991241756</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588390330398871</v>
+        <v>0.7515254801015665</v>
       </c>
       <c r="G19" t="n">
-        <v>20.79591715464427</v>
+        <v>23.56664942756468</v>
       </c>
       <c r="H19" t="n">
-        <v>37.25953419868974</v>
+        <v>37.9072102695236</v>
       </c>
       <c r="I19" t="n">
-        <v>1.512567000969649</v>
+        <v>1.776165458775121</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742743956499294</v>
+        <v>4.69703425063479</v>
       </c>
       <c r="K19" t="n">
-        <v>21.85412604804682</v>
+        <v>17.83990694753726</v>
       </c>
       <c r="L19" t="n">
-        <v>43.4867879356968</v>
+        <v>44.34845197044321</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94961360873999</v>
+        <v>99.94083711816585</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.48867561563875</v>
+        <v>79.21716686430433</v>
       </c>
       <c r="C20" t="n">
-        <v>32.18390920961475</v>
+        <v>35.08344653242291</v>
       </c>
       <c r="D20" t="n">
-        <v>1.122318171531752</v>
+        <v>1.243016922330525</v>
       </c>
       <c r="E20" t="n">
-        <v>11.14505635312951</v>
+        <v>11.40316259260232</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592616255201861</v>
+        <v>0.7519938358918699</v>
       </c>
       <c r="G20" t="n">
-        <v>19.17519606737891</v>
+        <v>21.70713742407876</v>
       </c>
       <c r="H20" t="n">
-        <v>37.2802837889009</v>
+        <v>37.93083430076945</v>
       </c>
       <c r="I20" t="n">
-        <v>1.261174449676342</v>
+        <v>1.481060314307235</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745385159501163</v>
+        <v>4.699961474324185</v>
       </c>
       <c r="K20" t="n">
-        <v>24.51132438436124</v>
+        <v>20.78283313569566</v>
       </c>
       <c r="L20" t="n">
-        <v>43.26275065599707</v>
+        <v>44.08438240247098</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95798424997307</v>
+        <v>99.95066207058956</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.48224535006554</v>
+        <v>76.28171177617524</v>
       </c>
       <c r="C21" t="n">
-        <v>35.86380238877432</v>
+        <v>32.37555850820595</v>
       </c>
       <c r="D21" t="n">
-        <v>1.123170273618322</v>
+        <v>1.13741585904902</v>
       </c>
       <c r="E21" t="n">
-        <v>13.14055351282711</v>
+        <v>10.64021559309756</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598380827421832</v>
+        <v>0.7523996231289884</v>
       </c>
       <c r="G21" t="n">
-        <v>20.86746953683241</v>
+        <v>19.86299777352384</v>
       </c>
       <c r="H21" t="n">
-        <v>38.98630325607265</v>
+        <v>37.95130235212556</v>
       </c>
       <c r="I21" t="n">
-        <v>1.855922670834232</v>
+        <v>1.234882930694105</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748988017138646</v>
+        <v>4.702497644556177</v>
       </c>
       <c r="K21" t="n">
-        <v>18.51775464993447</v>
+        <v>23.71828822382475</v>
       </c>
       <c r="L21" t="n">
-        <v>45.55662580594798</v>
+        <v>43.865012703683</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93818284465675</v>
+        <v>99.95885943571369</v>
       </c>
     </row>
   </sheetData>
